--- a/fx_pipeline/data/gold/marts/excel/gold_daily_currency_rates.xlsx
+++ b/fx_pipeline/data/gold/marts/excel/gold_daily_currency_rates.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:F115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,23 +448,13 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>load_batch_id</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>endpoint_name</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>response_status</t>
+          <t>batch_id</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -477,28 +467,20 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.4245</v>
+        <v>1.439</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -511,28 +493,20 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.3708</v>
+        <v>1.3749</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -545,28 +519,20 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.86237</v>
+        <v>0.86415</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -579,28 +545,20 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.74526</v>
+        <v>0.74785</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -613,28 +571,20 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>93.22</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -647,28 +597,20 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>158.55</v>
+        <v>158.93</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -681,28 +623,20 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.439</v>
+        <v>1.4361</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -715,28 +649,20 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.3749</v>
+        <v>1.3783</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -749,28 +675,20 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.86415</v>
+        <v>0.86266</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -783,28 +701,20 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.74785</v>
+        <v>0.7467</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -817,28 +727,20 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>93.84999999999999</v>
+        <v>93.94</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -851,28 +753,20 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>158.93</v>
+        <v>158.96</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -885,28 +779,20 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.4361</v>
+        <v>1.4467</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -919,28 +805,20 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.3783</v>
+        <v>1.3835</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -953,28 +831,20 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.86266</v>
+        <v>0.86663</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -987,28 +857,20 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.7467</v>
+        <v>0.74976</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1021,28 +883,20 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>93.94</v>
+        <v>94.12</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1055,28 +909,20 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>158.96</v>
+        <v>159.62</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1089,28 +935,20 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.4467</v>
+        <v>1.4527</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1123,28 +961,20 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1.3835</v>
+        <v>1.387</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1157,28 +987,20 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.86663</v>
+        <v>0.8682800000000001</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1191,28 +1013,20 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.74976</v>
+        <v>0.75297</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1225,28 +1039,20 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>94.12</v>
+        <v>94.81</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1259,28 +1065,20 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>159.62</v>
+        <v>159.9</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1293,28 +1091,20 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1.4527</v>
+        <v>1.4577</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1327,28 +1117,20 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1.387</v>
+        <v>1.3921</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1361,28 +1143,20 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.8682800000000001</v>
+        <v>0.87078</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1395,28 +1169,20 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.75297</v>
+        <v>0.75586</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1429,28 +1195,20 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>94.81</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1463,28 +1221,20 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>159.9</v>
+        <v>159.46</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1497,28 +1247,20 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.4577</v>
+        <v>1.4518</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1531,28 +1273,20 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1.3921</v>
+        <v>1.3935</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1565,28 +1299,20 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.87078</v>
+        <v>0.86972</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1599,28 +1325,20 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.75586</v>
+        <v>0.7552</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1633,28 +1351,20 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>94.70999999999999</v>
+        <v>93.83</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1667,28 +1377,20 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>159.46</v>
+        <v>159.5</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1701,28 +1403,20 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1.4518</v>
+        <v>1.4381</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1735,28 +1429,20 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1.3935</v>
+        <v>1.3894</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1769,28 +1455,20 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.86972</v>
+        <v>0.8617</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1803,28 +1481,20 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.7552</v>
+        <v>0.75065</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1837,28 +1507,20 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>93.83</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H42" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1871,28 +1533,20 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>159.5</v>
+        <v>158.32</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1905,28 +1559,20 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1.4381</v>
+        <v>1.4552</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1939,28 +1585,20 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1.3894</v>
+        <v>1.3909</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -1973,28 +1611,20 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.8617</v>
+        <v>0.86768</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H46" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2007,28 +1637,20 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.75065</v>
+        <v>0.75708</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H47" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2041,28 +1663,20 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>93.43000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2075,28 +1689,20 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>158.32</v>
+        <v>159.6</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H49" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2109,28 +1715,20 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.4552</v>
+        <v>1.442</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H50" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2143,28 +1741,20 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1.3909</v>
+        <v>1.3912</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2177,28 +1767,20 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.86768</v>
+        <v>0.86528</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2211,28 +1793,20 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.75708</v>
+        <v>0.75502</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2245,28 +1819,20 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>93.09999999999999</v>
+        <v>93.01000000000001</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H54" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2279,28 +1845,20 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>159.6</v>
+        <v>159.84</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H55" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2313,28 +1871,20 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1.442</v>
+        <v>1.4171</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H56" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2347,28 +1897,20 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1.3912</v>
+        <v>1.386</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H57" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2381,28 +1923,20 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.86528</v>
+        <v>0.85426</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H58" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2415,28 +1949,20 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.75502</v>
+        <v>0.74229</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H59" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2449,28 +1975,20 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>93.01000000000001</v>
+        <v>92.22</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H60" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2483,28 +2001,20 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>159.84</v>
+        <v>158.15</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H61" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2517,28 +2027,20 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1.4171</v>
+        <v>1.42</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H62" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2551,28 +2053,20 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1.386</v>
+        <v>1.3843</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H63" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2585,28 +2079,20 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.85426</v>
+        <v>0.8558</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H64" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -2619,28 +2105,20 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.74229</v>
+        <v>0.745</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H65" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -2653,28 +2131,20 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>92.22</v>
+        <v>92.66</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H66" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -2687,28 +2157,20 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>158.15</v>
+        <v>158.92</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H67" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -2721,28 +2183,20 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1.42</v>
+        <v>1.4141</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H68" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -2755,28 +2209,20 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1.3843</v>
+        <v>1.3822</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H69" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -2789,28 +2235,20 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.8558</v>
+        <v>0.8539</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H70" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -2823,28 +2261,20 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.745</v>
+        <v>0.74379</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H71" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -2857,28 +2287,20 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>92.66</v>
+        <v>92.89</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H72" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -2891,28 +2313,20 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>158.92</v>
+        <v>159.19</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H73" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -2925,28 +2339,20 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1.4141</v>
+        <v>1.4216</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H74" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -2959,28 +2365,20 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1.3822</v>
+        <v>1.3845</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H75" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -2993,28 +2391,20 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.8539</v>
+        <v>0.85587</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H76" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -3027,28 +2417,20 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.74379</v>
+        <v>0.7451</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H77" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -3061,28 +2443,20 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>92.89</v>
+        <v>93.33</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H78" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -3095,28 +2469,20 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>159.19</v>
+        <v>159.83</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H79" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -3129,28 +2495,20 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1.4216</v>
+        <v>1.4041</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H80" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -3163,28 +2521,20 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1.3845</v>
+        <v>1.3758</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H81" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -3197,28 +2547,20 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.85587</v>
+        <v>0.84796</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H82" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -3231,28 +2573,20 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.7451</v>
+        <v>0.73699</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H83" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -3265,28 +2599,20 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>93.33</v>
+        <v>93.09</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H84" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -3299,28 +2625,20 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>159.83</v>
+        <v>158.85</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H85" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -3333,28 +2651,20 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1.4041</v>
+        <v>1.4013</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H86" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -3367,28 +2677,20 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1.3758</v>
+        <v>1.3782</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H87" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -3401,28 +2703,20 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.84796</v>
+        <v>0.8489</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H88" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -3435,28 +2729,20 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.73699</v>
+        <v>0.73799</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H89" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -3469,28 +2755,20 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>93.09</v>
+        <v>93.44</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H90" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -3503,28 +2781,20 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>158.85</v>
+        <v>159.09</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H91" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -3537,28 +2807,20 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1.4013</v>
+        <v>1.3941</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H92" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -3571,28 +2833,20 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1.3782</v>
+        <v>1.3728</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H93" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -3605,28 +2859,20 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.8489</v>
+        <v>0.84875</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H94" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -3639,28 +2885,20 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.73799</v>
+        <v>0.73836</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H95" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -3673,28 +2911,20 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>93.44</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H96" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -3707,28 +2937,20 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>159.09</v>
+        <v>158.98</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H97" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -3741,28 +2963,20 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1.3941</v>
+        <v>1.3934</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H98" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -3775,28 +2989,20 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1.3728</v>
+        <v>1.3672</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H99" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -3809,28 +3015,20 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.84875</v>
+        <v>0.84767</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H100" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -3843,28 +3041,20 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.73836</v>
+        <v>0.7389</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H101" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -3877,28 +3067,20 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>93.23999999999999</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H102" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -3911,28 +3093,20 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>158.98</v>
+        <v>159.13</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H103" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -3945,28 +3119,20 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1.3934</v>
+        <v>1.3973</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H104" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -3979,28 +3145,20 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1.3672</v>
+        <v>1.3695</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H105" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -4013,28 +3171,20 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.84767</v>
+        <v>0.85034</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H106" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -4047,28 +3197,20 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.7389</v>
+        <v>0.7401799999999999</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H107" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -4081,28 +3223,20 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>92.81999999999999</v>
+        <v>93.06999999999999</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H108" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -4115,23 +3249,171 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>159.13</v>
+        <v>158.91</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H109" t="n">
-        <v>200</v>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>1.3957</v>
+      </c>
+      <c r="E110" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>1.3657</v>
+      </c>
+      <c r="E111" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0.84983</v>
+      </c>
+      <c r="E112" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>0.73965</v>
+      </c>
+      <c r="E113" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>93.51000000000001</v>
+      </c>
+      <c r="E114" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>159.04</v>
+      </c>
+      <c r="E115" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
       </c>
     </row>
   </sheetData>
